--- a/data/exports/predictions/lotto_predictions.xlsx
+++ b/data/exports/predictions/lotto_predictions.xlsx
@@ -552,7 +552,7 @@
         <v>2</v>
       </c>
       <c r="O2" t="n">
-        <v>7678.8674</v>
+        <v>7685.0558</v>
       </c>
       <c r="P2" t="n">
         <v>95</v>
@@ -564,7 +564,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-05-23 08:16:02</t>
+          <t>2026-05-24 05:27:54</t>
         </is>
       </c>
     </row>
@@ -576,31 +576,31 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D3" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E3" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F3" t="n">
+        <v>40</v>
+      </c>
+      <c r="G3" t="n">
         <v>44</v>
       </c>
-      <c r="G3" t="n">
-        <v>49</v>
-      </c>
       <c r="H3" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="I3" t="n">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="J3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L3" t="n">
         <v>3</v>
@@ -612,10 +612,10 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>7676.3119</v>
+        <v>7677.692</v>
       </c>
       <c r="P3" t="n">
-        <v>94.98999999999999</v>
+        <v>94.97</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -624,7 +624,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-05-23 08:16:02</t>
+          <t>2026-05-24 05:27:54</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>7664.4824</v>
+        <v>7669.0597</v>
       </c>
       <c r="P4" t="n">
         <v>94.93000000000001</v>
@@ -684,7 +684,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-05-23 08:16:02</t>
+          <t>2026-05-24 05:27:54</t>
         </is>
       </c>
     </row>
@@ -693,13 +693,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E5" t="n">
         <v>33</v>
@@ -708,13 +708,13 @@
         <v>40</v>
       </c>
       <c r="G5" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="H5" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="I5" t="n">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="J5" t="n">
         <v>3</v>
@@ -729,13 +729,13 @@
         <v>3</v>
       </c>
       <c r="N5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>7662.6645</v>
+        <v>7667.8354</v>
       </c>
       <c r="P5" t="n">
-        <v>94.93000000000001</v>
+        <v>94.92</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-05-23 08:16:02</t>
+          <t>2026-05-24 05:27:54</t>
         </is>
       </c>
     </row>
@@ -753,34 +753,34 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C6" t="n">
         <v>8</v>
       </c>
       <c r="D6" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="E6" t="n">
+        <v>33</v>
+      </c>
+      <c r="F6" t="n">
+        <v>40</v>
+      </c>
+      <c r="G6" t="n">
+        <v>43</v>
+      </c>
+      <c r="H6" t="n">
         <v>20</v>
       </c>
-      <c r="F6" t="n">
-        <v>33</v>
-      </c>
-      <c r="G6" t="n">
-        <v>49</v>
-      </c>
-      <c r="H6" t="n">
-        <v>28</v>
-      </c>
       <c r="I6" t="n">
-        <v>129</v>
+        <v>155</v>
       </c>
       <c r="J6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L6" t="n">
         <v>3</v>
@@ -792,10 +792,10 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>7656.4681</v>
+        <v>7667.3626</v>
       </c>
       <c r="P6" t="n">
-        <v>94.90000000000001</v>
+        <v>94.92</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-05-23 08:16:02</t>
+          <t>2026-05-24 05:27:54</t>
         </is>
       </c>
     </row>
@@ -813,49 +813,49 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D7" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E7" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="F7" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G7" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H7" t="n">
+        <v>18</v>
+      </c>
+      <c r="I7" t="n">
+        <v>149</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M7" t="n">
+        <v>3</v>
+      </c>
+      <c r="N7" t="n">
         <v>1</v>
       </c>
-      <c r="I7" t="n">
-        <v>153</v>
-      </c>
-      <c r="J7" t="n">
-        <v>2</v>
-      </c>
-      <c r="K7" t="n">
-        <v>4</v>
-      </c>
-      <c r="L7" t="n">
-        <v>3</v>
-      </c>
-      <c r="M7" t="n">
-        <v>3</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
       <c r="O7" t="n">
-        <v>7649.1602</v>
+        <v>7666.3121</v>
       </c>
       <c r="P7" t="n">
-        <v>94.86</v>
+        <v>94.91</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-05-23 08:16:02</t>
+          <t>2026-05-24 05:27:54</t>
         </is>
       </c>
     </row>
@@ -873,28 +873,28 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D8" t="n">
         <v>27</v>
       </c>
       <c r="E8" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F8" t="n">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G8" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H8" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I8" t="n">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="J8" t="n">
         <v>3</v>
@@ -909,13 +909,13 @@
         <v>3</v>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>7648.8886</v>
+        <v>7656.9049</v>
       </c>
       <c r="P8" t="n">
-        <v>94.86</v>
+        <v>94.87</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-05-23 08:16:02</t>
+          <t>2026-05-24 05:27:54</t>
         </is>
       </c>
     </row>
@@ -936,25 +936,25 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D9" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="E9" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F9" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="G9" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="H9" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="I9" t="n">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="J9" t="n">
         <v>3</v>
@@ -972,10 +972,10 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>7648.5621</v>
+        <v>7656.0384</v>
       </c>
       <c r="P9" t="n">
-        <v>94.86</v>
+        <v>94.87</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-05-23 08:16:02</t>
+          <t>2026-05-24 05:27:54</t>
         </is>
       </c>
     </row>
@@ -993,28 +993,28 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="E10" t="n">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="F10" t="n">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="G10" t="n">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="H10" t="n">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="I10" t="n">
-        <v>127</v>
+        <v>163</v>
       </c>
       <c r="J10" t="n">
         <v>3</v>
@@ -1029,13 +1029,13 @@
         <v>3</v>
       </c>
       <c r="N10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O10" t="n">
-        <v>7648.0371</v>
+        <v>7647.8924</v>
       </c>
       <c r="P10" t="n">
-        <v>94.86</v>
+        <v>94.83</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-05-23 08:16:02</t>
+          <t>2026-05-24 05:27:54</t>
         </is>
       </c>
     </row>
@@ -1056,10 +1056,10 @@
         <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D11" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="E11" t="n">
         <v>30</v>
@@ -1068,13 +1068,13 @@
         <v>32</v>
       </c>
       <c r="G11" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H11" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I11" t="n">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="J11" t="n">
         <v>3</v>
@@ -1089,13 +1089,13 @@
         <v>3</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O11" t="n">
-        <v>7645.1974</v>
+        <v>7647.8005</v>
       </c>
       <c r="P11" t="n">
-        <v>94.84999999999999</v>
+        <v>94.83</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-05-23 08:16:02</t>
+          <t>2026-05-24 05:27:54</t>
         </is>
       </c>
     </row>

--- a/data/exports/predictions/lotto_predictions.xlsx
+++ b/data/exports/predictions/lotto_predictions.xlsx
@@ -564,7 +564,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-05-24 05:27:54</t>
+          <t>2026-05-25 14:24:50</t>
         </is>
       </c>
     </row>
@@ -624,7 +624,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-05-24 05:27:54</t>
+          <t>2026-05-25 14:24:50</t>
         </is>
       </c>
     </row>
@@ -684,7 +684,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-05-24 05:27:54</t>
+          <t>2026-05-25 14:24:50</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-05-24 05:27:54</t>
+          <t>2026-05-25 14:24:50</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-05-24 05:27:54</t>
+          <t>2026-05-25 14:24:50</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-05-24 05:27:54</t>
+          <t>2026-05-25 14:24:50</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-05-24 05:27:54</t>
+          <t>2026-05-25 14:24:50</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-05-24 05:27:54</t>
+          <t>2026-05-25 14:24:50</t>
         </is>
       </c>
     </row>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-05-24 05:27:54</t>
+          <t>2026-05-25 14:24:50</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-05-24 05:27:54</t>
+          <t>2026-05-25 14:24:50</t>
         </is>
       </c>
     </row>

--- a/data/exports/predictions/lotto_predictions.xlsx
+++ b/data/exports/predictions/lotto_predictions.xlsx
@@ -564,7 +564,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-05-25 14:24:50</t>
+          <t>2026-05-26 14:15:37</t>
         </is>
       </c>
     </row>
@@ -624,7 +624,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-05-25 14:24:50</t>
+          <t>2026-05-26 14:15:37</t>
         </is>
       </c>
     </row>
@@ -684,7 +684,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-05-25 14:24:50</t>
+          <t>2026-05-26 14:15:37</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-05-25 14:24:50</t>
+          <t>2026-05-26 14:15:37</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-05-25 14:24:50</t>
+          <t>2026-05-26 14:15:37</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-05-25 14:24:50</t>
+          <t>2026-05-26 14:15:37</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-05-25 14:24:50</t>
+          <t>2026-05-26 14:15:37</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-05-25 14:24:50</t>
+          <t>2026-05-26 14:15:37</t>
         </is>
       </c>
     </row>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-05-25 14:24:50</t>
+          <t>2026-05-26 14:15:37</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-05-25 14:24:50</t>
+          <t>2026-05-26 14:15:37</t>
         </is>
       </c>
     </row>

--- a/data/exports/predictions/lotto_predictions.xlsx
+++ b/data/exports/predictions/lotto_predictions.xlsx
@@ -564,7 +564,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-05-26 14:15:37</t>
+          <t>2026-05-27 14:49:09</t>
         </is>
       </c>
     </row>
@@ -624,7 +624,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-05-26 14:15:37</t>
+          <t>2026-05-27 14:49:09</t>
         </is>
       </c>
     </row>
@@ -684,7 +684,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-05-26 14:15:37</t>
+          <t>2026-05-27 14:49:09</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-05-26 14:15:37</t>
+          <t>2026-05-27 14:49:09</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-05-26 14:15:37</t>
+          <t>2026-05-27 14:49:09</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-05-26 14:15:37</t>
+          <t>2026-05-27 14:49:09</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-05-26 14:15:37</t>
+          <t>2026-05-27 14:49:09</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-05-26 14:15:37</t>
+          <t>2026-05-27 14:49:09</t>
         </is>
       </c>
     </row>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-05-26 14:15:37</t>
+          <t>2026-05-27 14:49:09</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-05-26 14:15:37</t>
+          <t>2026-05-27 14:49:09</t>
         </is>
       </c>
     </row>

--- a/data/exports/predictions/lotto_predictions.xlsx
+++ b/data/exports/predictions/lotto_predictions.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R11"/>
+  <dimension ref="A1:W11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -484,25 +484,50 @@
       </c>
       <c r="N1" t="inlineStr">
         <is>
+          <t>Bucket_LOW</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Bucket_MID_LOW</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Bucket_MID_HIGH</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>Bucket_HIGH</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>Upper50PlusCount</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
           <t>ConsecutivePairs</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>RawScore</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Confidence</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>ModelVersion</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>GeneratedAt</t>
         </is>
@@ -513,28 +538,28 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="E2" t="n">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="F2" t="n">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="G2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H2" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="I2" t="n">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="J2" t="n">
         <v>3</v>
@@ -552,19 +577,34 @@
         <v>2</v>
       </c>
       <c r="O2" t="n">
-        <v>7685.0558</v>
+        <v>1</v>
       </c>
       <c r="P2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3453.434</v>
+      </c>
+      <c r="U2" t="n">
         <v>95</v>
       </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>Lotto_v1_statistical</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>2026-05-27 14:49:09</t>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Lotto_v2_range_balanced</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:47:26</t>
         </is>
       </c>
     </row>
@@ -573,34 +613,34 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C3" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D3" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E3" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F3" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="G3" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H3" t="n">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="I3" t="n">
-        <v>153</v>
+        <v>169</v>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L3" t="n">
         <v>3</v>
@@ -609,22 +649,37 @@
         <v>3</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O3" t="n">
-        <v>7677.692</v>
+        <v>1</v>
       </c>
       <c r="P3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3450.3437</v>
+      </c>
+      <c r="U3" t="n">
         <v>94.97</v>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>Lotto_v1_statistical</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>2026-05-27 14:49:09</t>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Lotto_v2_range_balanced</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:47:26</t>
         </is>
       </c>
     </row>
@@ -636,25 +691,25 @@
         <v>4</v>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E4" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="F4" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="G4" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="H4" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="I4" t="n">
-        <v>153</v>
+        <v>169</v>
       </c>
       <c r="J4" t="n">
         <v>3</v>
@@ -669,22 +724,37 @@
         <v>3</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O4" t="n">
-        <v>7669.0597</v>
+        <v>1</v>
       </c>
       <c r="P4" t="n">
-        <v>94.93000000000001</v>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>Lotto_v1_statistical</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>2026-05-27 14:49:09</t>
+        <v>2</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3450.081</v>
+      </c>
+      <c r="U4" t="n">
+        <v>94.97</v>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Lotto_v2_range_balanced</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:47:26</t>
         </is>
       </c>
     </row>
@@ -693,28 +763,28 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
         <v>29</v>
       </c>
       <c r="E5" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="F5" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G5" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="H5" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="I5" t="n">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="J5" t="n">
         <v>3</v>
@@ -729,22 +799,37 @@
         <v>3</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O5" t="n">
-        <v>7667.8354</v>
+        <v>1</v>
       </c>
       <c r="P5" t="n">
-        <v>94.92</v>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>Lotto_v1_statistical</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>2026-05-27 14:49:09</t>
+        <v>2</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3449.7961</v>
+      </c>
+      <c r="U5" t="n">
+        <v>94.95999999999999</v>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Lotto_v2_range_balanced</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:47:26</t>
         </is>
       </c>
     </row>
@@ -753,13 +838,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C6" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E6" t="n">
         <v>33</v>
@@ -768,13 +853,13 @@
         <v>40</v>
       </c>
       <c r="G6" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="H6" t="n">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="I6" t="n">
-        <v>155</v>
+        <v>169</v>
       </c>
       <c r="J6" t="n">
         <v>3</v>
@@ -789,22 +874,37 @@
         <v>3</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O6" t="n">
-        <v>7667.3626</v>
+        <v>1</v>
       </c>
       <c r="P6" t="n">
-        <v>94.92</v>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>Lotto_v1_statistical</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>2026-05-27 14:49:09</t>
+        <v>2</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3448.0581</v>
+      </c>
+      <c r="U6" t="n">
+        <v>94.95</v>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Lotto_v2_range_balanced</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:47:26</t>
         </is>
       </c>
     </row>
@@ -813,28 +913,28 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C7" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D7" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="E7" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F7" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G7" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="H7" t="n">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I7" t="n">
-        <v>149</v>
+        <v>173</v>
       </c>
       <c r="J7" t="n">
         <v>3</v>
@@ -849,22 +949,37 @@
         <v>3</v>
       </c>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O7" t="n">
-        <v>7666.3121</v>
+        <v>1</v>
       </c>
       <c r="P7" t="n">
-        <v>94.91</v>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>Lotto_v1_statistical</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>2026-05-27 14:49:09</t>
+        <v>2</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3446.4091</v>
+      </c>
+      <c r="U7" t="n">
+        <v>94.93000000000001</v>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Lotto_v2_range_balanced</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:47:26</t>
         </is>
       </c>
     </row>
@@ -873,28 +988,28 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D8" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="E8" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="F8" t="n">
         <v>42</v>
       </c>
       <c r="G8" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="H8" t="n">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="I8" t="n">
-        <v>155</v>
+        <v>169</v>
       </c>
       <c r="J8" t="n">
         <v>3</v>
@@ -909,22 +1024,37 @@
         <v>3</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O8" t="n">
-        <v>7656.9049</v>
+        <v>1</v>
       </c>
       <c r="P8" t="n">
-        <v>94.87</v>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>Lotto_v1_statistical</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>2026-05-27 14:49:09</t>
+        <v>2</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3446.2438</v>
+      </c>
+      <c r="U8" t="n">
+        <v>94.93000000000001</v>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Lotto_v2_range_balanced</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:47:26</t>
         </is>
       </c>
     </row>
@@ -933,28 +1063,28 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D9" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E9" t="n">
         <v>30</v>
       </c>
       <c r="F9" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="G9" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H9" t="n">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="I9" t="n">
-        <v>165</v>
+        <v>147</v>
       </c>
       <c r="J9" t="n">
         <v>3</v>
@@ -969,22 +1099,37 @@
         <v>3</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O9" t="n">
-        <v>7656.0384</v>
+        <v>1</v>
       </c>
       <c r="P9" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3440.5184</v>
+      </c>
+      <c r="U9" t="n">
         <v>94.87</v>
       </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>Lotto_v1_statistical</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>2026-05-27 14:49:09</t>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Lotto_v2_range_balanced</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:47:26</t>
         </is>
       </c>
     </row>
@@ -993,28 +1138,28 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D10" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E10" t="n">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="F10" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="G10" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H10" t="n">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="I10" t="n">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="J10" t="n">
         <v>3</v>
@@ -1032,19 +1177,34 @@
         <v>2</v>
       </c>
       <c r="O10" t="n">
-        <v>7647.8924</v>
+        <v>1</v>
       </c>
       <c r="P10" t="n">
-        <v>94.83</v>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>Lotto_v1_statistical</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>2026-05-27 14:49:09</t>
+        <v>2</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3439.9283</v>
+      </c>
+      <c r="U10" t="n">
+        <v>94.86</v>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Lotto_v2_range_balanced</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:47:26</t>
         </is>
       </c>
     </row>
@@ -1053,28 +1213,28 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D11" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E11" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="F11" t="n">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="G11" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H11" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="I11" t="n">
-        <v>137</v>
+        <v>163</v>
       </c>
       <c r="J11" t="n">
         <v>3</v>
@@ -1089,22 +1249,37 @@
         <v>3</v>
       </c>
       <c r="N11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O11" t="n">
-        <v>7647.8005</v>
+        <v>1</v>
       </c>
       <c r="P11" t="n">
-        <v>94.83</v>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>Lotto_v1_statistical</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>2026-05-27 14:49:09</t>
+        <v>2</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3437.961</v>
+      </c>
+      <c r="U11" t="n">
+        <v>94.84</v>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Lotto_v2_range_balanced</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:47:26</t>
         </is>
       </c>
     </row>

--- a/data/exports/predictions/lotto_predictions.xlsx
+++ b/data/exports/predictions/lotto_predictions.xlsx
@@ -538,7 +538,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C2" t="n">
         <v>12</v>
@@ -547,7 +547,7 @@
         <v>22</v>
       </c>
       <c r="E2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F2" t="n">
         <v>37</v>
@@ -556,10 +556,10 @@
         <v>49</v>
       </c>
       <c r="H2" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="I2" t="n">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="J2" t="n">
         <v>3</v>
@@ -589,10 +589,10 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T2" t="n">
-        <v>3453.434</v>
+        <v>3462.313</v>
       </c>
       <c r="U2" t="n">
         <v>95</v>
@@ -604,7 +604,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2026-05-28 08:47:26</t>
+          <t>2026-05-28 17:13:18</t>
         </is>
       </c>
     </row>
@@ -613,28 +613,28 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C3" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D3" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E3" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F3" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G3" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H3" t="n">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="I3" t="n">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="J3" t="n">
         <v>3</v>
@@ -664,13 +664,13 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>3450.3437</v>
+        <v>3458.1908</v>
       </c>
       <c r="U3" t="n">
-        <v>94.97</v>
+        <v>94.95999999999999</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
@@ -679,7 +679,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2026-05-28 08:47:26</t>
+          <t>2026-05-28 17:13:18</t>
         </is>
       </c>
     </row>
@@ -688,28 +688,28 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D4" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E4" t="n">
+        <v>32</v>
+      </c>
+      <c r="F4" t="n">
         <v>39</v>
       </c>
-      <c r="F4" t="n">
-        <v>44</v>
-      </c>
       <c r="G4" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I4" t="n">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="J4" t="n">
         <v>3</v>
@@ -742,10 +742,10 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>3450.081</v>
+        <v>3455.4015</v>
       </c>
       <c r="U4" t="n">
-        <v>94.97</v>
+        <v>94.93000000000001</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
@@ -754,7 +754,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2026-05-28 08:47:26</t>
+          <t>2026-05-28 17:13:18</t>
         </is>
       </c>
     </row>
@@ -763,28 +763,28 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E5" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F5" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G5" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="H5" t="n">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="I5" t="n">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="J5" t="n">
         <v>3</v>
@@ -814,13 +814,13 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>3449.7961</v>
+        <v>3454.8044</v>
       </c>
       <c r="U5" t="n">
-        <v>94.95999999999999</v>
+        <v>94.92</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
@@ -829,7 +829,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2026-05-28 08:47:26</t>
+          <t>2026-05-28 17:13:18</t>
         </is>
       </c>
     </row>
@@ -838,25 +838,25 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D6" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E6" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="F6" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G6" t="n">
         <v>47</v>
       </c>
       <c r="H6" t="n">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="I6" t="n">
         <v>169</v>
@@ -892,10 +892,10 @@
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3448.0581</v>
+        <v>3454.1313</v>
       </c>
       <c r="U6" t="n">
-        <v>94.95</v>
+        <v>94.92</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2026-05-28 08:47:26</t>
+          <t>2026-05-28 17:13:18</t>
         </is>
       </c>
     </row>
@@ -913,28 +913,28 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C7" t="n">
         <v>12</v>
       </c>
       <c r="D7" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E7" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F7" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G7" t="n">
         <v>49</v>
       </c>
       <c r="H7" t="n">
-        <v>43</v>
+        <v>9</v>
       </c>
       <c r="I7" t="n">
-        <v>173</v>
+        <v>153</v>
       </c>
       <c r="J7" t="n">
         <v>3</v>
@@ -964,13 +964,13 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3446.4091</v>
+        <v>3453.6855</v>
       </c>
       <c r="U7" t="n">
-        <v>94.93000000000001</v>
+        <v>94.91</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2026-05-28 08:47:26</t>
+          <t>2026-05-28 17:13:18</t>
         </is>
       </c>
     </row>
@@ -988,28 +988,28 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D8" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="E8" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="F8" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G8" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H8" t="n">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="I8" t="n">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="J8" t="n">
         <v>3</v>
@@ -1039,13 +1039,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3446.2438</v>
+        <v>3453.6489</v>
       </c>
       <c r="U8" t="n">
-        <v>94.93000000000001</v>
+        <v>94.91</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>2026-05-28 08:47:26</t>
+          <t>2026-05-28 17:13:18</t>
         </is>
       </c>
     </row>
@@ -1063,28 +1063,28 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D9" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E9" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F9" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="G9" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="H9" t="n">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="I9" t="n">
-        <v>147</v>
+        <v>161</v>
       </c>
       <c r="J9" t="n">
         <v>3</v>
@@ -1117,10 +1117,10 @@
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>3440.5184</v>
+        <v>3452.5291</v>
       </c>
       <c r="U9" t="n">
-        <v>94.87</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>2026-05-28 08:47:26</t>
+          <t>2026-05-28 17:13:18</t>
         </is>
       </c>
     </row>
@@ -1138,13 +1138,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D10" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="E10" t="n">
         <v>32</v>
@@ -1156,10 +1156,10 @@
         <v>49</v>
       </c>
       <c r="H10" t="n">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="I10" t="n">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="J10" t="n">
         <v>3</v>
@@ -1174,10 +1174,10 @@
         <v>3</v>
       </c>
       <c r="N10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P10" t="n">
         <v>2</v>
@@ -1192,10 +1192,10 @@
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>3439.9283</v>
+        <v>3451.4822</v>
       </c>
       <c r="U10" t="n">
-        <v>94.86</v>
+        <v>94.89</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>2026-05-28 08:47:26</t>
+          <t>2026-05-28 17:13:18</t>
         </is>
       </c>
     </row>
@@ -1213,28 +1213,28 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D11" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E11" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="F11" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G11" t="n">
         <v>48</v>
       </c>
       <c r="H11" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="I11" t="n">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="J11" t="n">
         <v>3</v>
@@ -1267,10 +1267,10 @@
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>3437.961</v>
+        <v>3450.5686</v>
       </c>
       <c r="U11" t="n">
-        <v>94.84</v>
+        <v>94.88</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>2026-05-28 08:47:26</t>
+          <t>2026-05-28 17:13:18</t>
         </is>
       </c>
     </row>

--- a/data/exports/predictions/lotto_predictions.xlsx
+++ b/data/exports/predictions/lotto_predictions.xlsx
@@ -604,7 +604,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2026-05-28 17:13:18</t>
+          <t>2026-05-28 19:42:58</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2026-05-28 17:13:18</t>
+          <t>2026-05-28 19:42:58</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2026-05-28 17:13:18</t>
+          <t>2026-05-28 19:42:58</t>
         </is>
       </c>
     </row>
@@ -829,7 +829,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2026-05-28 17:13:18</t>
+          <t>2026-05-28 19:42:58</t>
         </is>
       </c>
     </row>
@@ -904,7 +904,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2026-05-28 17:13:18</t>
+          <t>2026-05-28 19:42:58</t>
         </is>
       </c>
     </row>
@@ -979,7 +979,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2026-05-28 17:13:18</t>
+          <t>2026-05-28 19:42:58</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>2026-05-28 17:13:18</t>
+          <t>2026-05-28 19:42:58</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>2026-05-28 17:13:18</t>
+          <t>2026-05-28 19:42:58</t>
         </is>
       </c>
     </row>
@@ -1204,7 +1204,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>2026-05-28 17:13:18</t>
+          <t>2026-05-28 19:42:58</t>
         </is>
       </c>
     </row>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>2026-05-28 17:13:18</t>
+          <t>2026-05-28 19:42:58</t>
         </is>
       </c>
     </row>
